--- a/110-creation-exemples/ig/StructureDefinition-as-address-extended.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:21:44+00:00</t>
+    <t>2024-07-01T16:22:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-address-extended.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-address-extended.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="280">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T16:22:22+00:00</t>
+    <t>2024-07-02T08:22:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -484,19 +484,10 @@
     <t>Address.line.id</t>
   </si>
   <si>
-    <t>xml:id (or equivalent in JSON)</t>
-  </si>
-  <si>
-    <t>unique id for the element within a resource (for internal references)</t>
-  </si>
-  <si>
     <t>Address.line.extension</t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
+    <t>N/A</t>
   </si>
   <si>
     <t>Address.line.extension:careOf</t>
@@ -610,6 +601,12 @@
     <t>Address.line.extension.extension</t>
   </si>
   <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
     <t>Address.line.extension:streetNameType.url</t>
   </si>
   <si>
@@ -635,9 +632,6 @@
     <t>Extension.url</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Address.line.extension:streetNameType.value[x]</t>
   </si>
   <si>
@@ -718,9 +712,6 @@
   </si>
   <si>
     <t>Primitive value for string</t>
-  </si>
-  <si>
-    <t>The actual value</t>
   </si>
   <si>
     <t>1048576</t>
@@ -2319,10 +2310,10 @@
         <v>90</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>152</v>
+        <v>91</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>153</v>
+        <v>92</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2391,7 +2382,7 @@
         <v>77</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>77</v>
@@ -2402,14 +2393,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2431,12 +2422,14 @@
         <v>97</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>155</v>
+        <v>98</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>99</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>100</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -2475,7 +2468,9 @@
       <c r="AB11" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AC11" s="2"/>
+      <c r="AC11" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="AD11" t="s" s="2">
         <v>77</v>
       </c>
@@ -2492,7 +2487,7 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>105</v>
@@ -2501,7 +2496,7 @@
         <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -2512,13 +2507,13 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>77</v>
@@ -2540,13 +2535,13 @@
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2606,7 +2601,7 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>105</v>
@@ -2615,7 +2610,7 @@
         <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
@@ -2626,13 +2621,13 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>77</v>
@@ -2654,13 +2649,13 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2720,7 +2715,7 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>105</v>
@@ -2729,7 +2724,7 @@
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -2740,13 +2735,13 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>77</v>
@@ -2768,13 +2763,13 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2834,7 +2829,7 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>105</v>
@@ -2843,7 +2838,7 @@
         <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -2854,13 +2849,13 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>77</v>
@@ -2882,13 +2877,13 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2948,7 +2943,7 @@
         <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>105</v>
@@ -2957,7 +2952,7 @@
         <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -2968,13 +2963,13 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>77</v>
@@ -2996,13 +2991,13 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3062,7 +3057,7 @@
         <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>105</v>
@@ -3071,7 +3066,7 @@
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3082,10 +3077,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3108,7 +3103,7 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>91</v>
@@ -3194,10 +3189,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3223,10 +3218,10 @@
         <v>97</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>155</v>
+        <v>189</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>156</v>
+        <v>190</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3306,10 +3301,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3332,16 +3327,16 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3349,49 +3344,49 @@
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF19" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="S19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>89</v>
@@ -3409,7 +3404,7 @@
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>200</v>
+        <v>153</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3420,10 +3415,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3449,10 +3444,10 @@
         <v>90</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3483,7 +3478,7 @@
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>77</v>
@@ -3501,7 +3496,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3510,7 +3505,7 @@
         <v>89</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>85</v>
@@ -3519,7 +3514,7 @@
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>200</v>
+        <v>153</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -3530,13 +3525,13 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>77</v>
@@ -3558,13 +3553,13 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="L21" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3624,7 +3619,7 @@
         <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>105</v>
@@ -3633,7 +3628,7 @@
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -3644,13 +3639,13 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>77</v>
@@ -3672,13 +3667,13 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3738,7 +3733,7 @@
         <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>105</v>
@@ -3747,7 +3742,7 @@
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -3758,13 +3753,13 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>77</v>
@@ -3786,13 +3781,13 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3872,10 +3867,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3901,10 +3896,10 @@
         <v>90</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3928,7 +3923,7 @@
         <v>77</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="X24" t="s" s="2">
         <v>77</v>
@@ -3955,7 +3950,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -3984,14 +3979,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4013,10 +4008,10 @@
         <v>90</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4031,7 +4026,7 @@
         <v>77</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>77</v>
@@ -4067,7 +4062,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4082,28 +4077,28 @@
         <v>85</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>238</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4125,13 +4120,13 @@
         <v>90</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4145,7 +4140,7 @@
         <v>77</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>77</v>
@@ -4161,7 +4156,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>77</v>
@@ -4179,7 +4174,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4194,10 +4189,10 @@
         <v>85</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4208,14 +4203,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4237,10 +4232,10 @@
         <v>90</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4291,7 +4286,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4306,28 +4301,28 @@
         <v>85</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>255</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4349,10 +4344,10 @@
         <v>90</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4367,7 +4362,7 @@
         <v>77</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>77</v>
@@ -4403,7 +4398,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4418,24 +4413,24 @@
         <v>85</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>264</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4461,13 +4456,13 @@
         <v>90</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4497,7 +4492,7 @@
       </c>
       <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -4515,7 +4510,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4530,24 +4525,24 @@
         <v>85</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>273</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4570,17 +4565,17 @@
         <v>112</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -4593,7 +4588,7 @@
         <v>77</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="U30" t="s" s="2">
         <v>77</v>
@@ -4629,7 +4624,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4644,13 +4639,13 @@
         <v>85</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>

--- a/110-creation-exemples/ig/StructureDefinition-as-address-extended.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T08:22:21+00:00</t>
+    <t>2024-07-02T09:45:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-address-extended.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T09:45:37+00:00</t>
+    <t>2024-07-02T11:34:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-address-extended.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:34:04+00:00</t>
+    <t>2024-07-02T11:51:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-address-extended.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:51:09+00:00</t>
+    <t>2024-07-02T12:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-address-extended.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:01:26+00:00</t>
+    <t>2024-07-02T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-address-extended.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:28:16+00:00</t>
+    <t>2024-07-02T14:06:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-address-extended.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T14:06:23+00:00</t>
+    <t>2024-07-09T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-address-extended.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T09:28:43+00:00</t>
+    <t>2024-07-09T09:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
